--- a/FileRaw/FORNITORI Confident.xlsx
+++ b/FileRaw/FORNITORI Confident.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://confidentdental-my.sharepoint.com/personal/info_confident_dental/Documents/009 - BACKOFFICE (ILARIA + MELANIA)/014. vario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadepaoli/Documents/Coding/cDen/chipdent/FileRaw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1636" documentId="8_{209C4FF3-BC32-4981-BD9A-B58D7B754AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3047E860-7005-4436-95CA-A6698C65FD75}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E52529D-6A9A-E14B-AA1D-404D01460E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC632294-D196-4EA2-B74C-14E8F7613F9D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DC632294-D196-4EA2-B74C-14E8F7613F9D}"/>
   </bookViews>
   <sheets>
     <sheet name="fornitori" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="403">
   <si>
     <t xml:space="preserve">FORNITORI </t>
   </si>
@@ -245,9 +245,6 @@
     <t>Marco.Massa@unicreditleasing.eu</t>
   </si>
   <si>
-    <t>micheleh725@libero.it</t>
-  </si>
-  <si>
     <t>elisabetta.marseglia@vacondio.com</t>
   </si>
   <si>
@@ -650,474 +647,9 @@
     <t>affitto VAR</t>
   </si>
   <si>
-    <t>Alimova Mariya</t>
-  </si>
-  <si>
-    <t>alimova@live.it</t>
-  </si>
-  <si>
-    <t>Alorabi Khaled</t>
-  </si>
-  <si>
-    <t>khaled.alorabi@gmail.com</t>
-  </si>
-  <si>
-    <t>Alvarez Mark Joseph</t>
-  </si>
-  <si>
-    <t>markalvarez@icloud.com</t>
-  </si>
-  <si>
-    <t>Amato Armando</t>
-  </si>
-  <si>
-    <t>armact1969@gmail.com</t>
-  </si>
-  <si>
-    <t>Andolina Alessia</t>
-  </si>
-  <si>
-    <t>alessia.andolina@outlook.it</t>
-  </si>
-  <si>
-    <t>Arrigo Anna</t>
-  </si>
-  <si>
-    <t>anna_arrigo@hotmail.com</t>
-  </si>
-  <si>
-    <t>Arrigo Martina</t>
-  </si>
-  <si>
-    <t>martinarrigodoc@icloud.com</t>
-  </si>
-  <si>
-    <t>Baldi Carmen</t>
-  </si>
-  <si>
-    <t>carmenbaldi97@gmail.com</t>
-  </si>
-  <si>
-    <t>Battistini Chiara</t>
-  </si>
-  <si>
-    <t>chiabat.mi@gmail.com</t>
-  </si>
-  <si>
-    <t>Bertino Debora</t>
-  </si>
-  <si>
-    <t>deborabertino@hotmail.it</t>
-  </si>
-  <si>
-    <t>Bico Erblin</t>
-  </si>
-  <si>
-    <t>erblin.bico@gmail.com</t>
-  </si>
-  <si>
-    <t>Bonfanti Elisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> bonfanti.elisa15@gmail.com</t>
-  </si>
-  <si>
-    <t>Bruno Francesco</t>
-  </si>
-  <si>
-    <t>francesco.bruno9711@gmail.com</t>
-  </si>
-  <si>
-    <t>Borzì Valeria Giulia</t>
-  </si>
-  <si>
-    <t>valeriagiulia.borz@yahoo.it</t>
-  </si>
-  <si>
-    <t>Budelli Giacomo Giuseppe</t>
-  </si>
-  <si>
-    <t>Butera Vito</t>
-  </si>
-  <si>
-    <t>drbutera.vito@gmail.com</t>
-  </si>
-  <si>
-    <t>Campana Amirano</t>
-  </si>
-  <si>
-    <t>amiranocampana@libero.it</t>
-  </si>
-  <si>
-    <t>Capotosto Ilaria</t>
-  </si>
-  <si>
-    <t>ilaria.capotosto@hotmail.it</t>
-  </si>
-  <si>
-    <t>Cazzaniga Uberto Maria Pierugo</t>
-  </si>
-  <si>
-    <t>dottorcazzaniga80@gmail.com</t>
-  </si>
-  <si>
-    <t>Citterio Chiara</t>
-  </si>
-  <si>
-    <t>chiaracitt@gmail.com</t>
-  </si>
-  <si>
-    <t>Colitti Stefania</t>
-  </si>
-  <si>
-    <t>colittistefania@gmail.com</t>
-  </si>
-  <si>
-    <t>Colleoni Fabio</t>
-  </si>
-  <si>
-    <t>docfcolleoni@gmail.com</t>
-  </si>
-  <si>
-    <t>Colombo Chiara</t>
-  </si>
-  <si>
-    <t>colombo.chi@gmail.com</t>
-  </si>
-  <si>
-    <t>Conti Ilaria</t>
-  </si>
-  <si>
-    <t>conti.ilaria5@gmail.com</t>
-  </si>
-  <si>
-    <t>D'Anna Francesco</t>
-  </si>
-  <si>
-    <t>francesco.danna@odontoiatricorosmini.it</t>
-  </si>
-  <si>
-    <t>D'Apote Anna</t>
-  </si>
-  <si>
-    <t>anna.dapote.94@gmail.com</t>
-  </si>
-  <si>
-    <t>Del Col Gian Marco</t>
-  </si>
-  <si>
-    <t>gmdelcol@gmail.com</t>
-  </si>
-  <si>
-    <t>Di Francesco Matilde</t>
-  </si>
-  <si>
-    <t>difrancesco.matilde@gmail.com</t>
-  </si>
-  <si>
-    <t>D'Innella Eugenia</t>
-  </si>
-  <si>
-    <t>eugenia.dinnella@yahoo.it</t>
-  </si>
-  <si>
-    <t>Draganti Luca</t>
-  </si>
-  <si>
-    <t>luca.draganti@outlook.it</t>
-  </si>
-  <si>
-    <t>Elsherif Mohamed</t>
-  </si>
-  <si>
-    <t>mohamedfathi656656@gmail.com</t>
-  </si>
-  <si>
-    <t>Faranda Rosario</t>
-  </si>
-  <si>
-    <t>rosario.faranda1@gmail.com</t>
-  </si>
-  <si>
-    <t>Formenti Jacopo</t>
-  </si>
-  <si>
-    <t>jacopo.formenti@gmail.com</t>
-  </si>
-  <si>
-    <t>Giganti Alessandra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alessandra.giganti94@gmail.com </t>
-  </si>
-  <si>
-    <t>Hassan Naima Osman</t>
-  </si>
-  <si>
-    <t>osmanaima.hassan@gmail.com</t>
-  </si>
-  <si>
-    <t>Hodzic Nina</t>
-  </si>
-  <si>
-    <t>ninahodzic00@gmail.com</t>
-  </si>
-  <si>
-    <t>Jaffal Wassim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jaffalwassim@hotmail.com </t>
-  </si>
-  <si>
-    <t>Kamh Ahmed</t>
-  </si>
-  <si>
-    <t>ahmed.kamh125@gmail.com</t>
-  </si>
-  <si>
-    <t>Lanza Maurizio</t>
-  </si>
-  <si>
-    <t>mlanza@hotmail.it</t>
-  </si>
-  <si>
-    <t>Khalil Antounious</t>
-  </si>
-  <si>
-    <t>antonios.khalil@gmail.com</t>
-  </si>
-  <si>
-    <t>La Regina Gaetano</t>
-  </si>
-  <si>
-    <t>incisivo1@virgilio.it</t>
-  </si>
-  <si>
-    <t>Lazzari Giuseppe</t>
-  </si>
-  <si>
-    <t>gi.lazzari1959@gmail.com</t>
-  </si>
-  <si>
-    <t>Lerose Daniele</t>
-  </si>
-  <si>
-    <t>dani.lerose@virgilio.it</t>
-  </si>
-  <si>
-    <t>Maiere Daniele</t>
-  </si>
-  <si>
-    <t>d.maiere@libero.it</t>
-  </si>
-  <si>
-    <t>Malveda Mel Brenix</t>
-  </si>
-  <si>
-    <t>melbrenixmalveda10@gmail.com</t>
-  </si>
-  <si>
-    <t>Manganaro Giuseppe</t>
-  </si>
-  <si>
-    <t>g.manganaro15@gmail.com</t>
-  </si>
-  <si>
-    <t>Maranan Athena Mae</t>
-  </si>
-  <si>
-    <t>athena.maranan@gmail.com</t>
-  </si>
-  <si>
-    <t>Malavasi Roberto</t>
-  </si>
-  <si>
-    <t>malavasi@hotmail.it</t>
-  </si>
-  <si>
-    <t>Mazzullo Filippo Lupo</t>
-  </si>
-  <si>
-    <t>lupo.mazzullo@gmail.com</t>
-  </si>
-  <si>
-    <t>Monti Beatrice</t>
-  </si>
-  <si>
-    <t>beatricemonti86@gmail.com</t>
-  </si>
-  <si>
-    <t>Morsilli Marco</t>
-  </si>
-  <si>
-    <t>m.morsilli@gmail.com</t>
-  </si>
-  <si>
-    <t>Mucllari Silvano</t>
-  </si>
-  <si>
-    <t>silvanomucllari@gmail.com</t>
-  </si>
-  <si>
-    <t>Muscianisi Ilaria</t>
-  </si>
-  <si>
-    <t>i.muscianisi@hotmail.com</t>
-  </si>
-  <si>
-    <t>Novelli Giuliana</t>
-  </si>
-  <si>
-    <t>gnovelli59@libero.it</t>
-  </si>
-  <si>
-    <t>Orlando Benedetta</t>
-  </si>
-  <si>
-    <t>benedetta.orlando@hotmail.it</t>
-  </si>
-  <si>
-    <t>Ornago Laura</t>
-  </si>
-  <si>
-    <t>ornagolaura@gmail.com</t>
-  </si>
-  <si>
-    <t>Paglioli Edoardo</t>
-  </si>
-  <si>
-    <t>edoardo.paglioli1@gmail.com</t>
-  </si>
-  <si>
-    <t>Panizza Sergio</t>
-  </si>
-  <si>
-    <t>sergioptravel@gmail.com</t>
-  </si>
-  <si>
-    <t>Morsilli Alessandro</t>
-  </si>
-  <si>
-    <t>dott.morsilli@gmail.com</t>
-  </si>
-  <si>
-    <t>Paroni Lorenzo Piero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lorenzopiero.paroni@gmail.com </t>
-  </si>
-  <si>
-    <t>Piccirillo Giovan Battista</t>
-  </si>
-  <si>
-    <t>giovanbpiccirillo@gmail.com</t>
-  </si>
-  <si>
-    <t>Pisotti Chiara</t>
-  </si>
-  <si>
-    <t>chiarapisotti1994@gmail.com</t>
-  </si>
-  <si>
-    <t>Porcari Serena</t>
-  </si>
-  <si>
-    <t>porcari.serena@gmail.com</t>
-  </si>
-  <si>
-    <t>Pozzi Antonio Mario</t>
-  </si>
-  <si>
-    <t>antonio.pozzi1956@tiscali.it</t>
-  </si>
-  <si>
-    <t>Provenzano Daniele</t>
-  </si>
-  <si>
     <t>danprove@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Provenzano Pasquale Antonio </t>
-  </si>
-  <si>
-    <t>paprove59@gmail.com</t>
-  </si>
-  <si>
-    <t>Rigobello Matteo Maria</t>
-  </si>
-  <si>
-    <t>matteorigobello4@gmail.com</t>
-  </si>
-  <si>
-    <t>Rodilosso Giorgia</t>
-  </si>
-  <si>
-    <t>gio.rodilosso@gmail.com</t>
-  </si>
-  <si>
-    <t>Roganti Paolo</t>
-  </si>
-  <si>
-    <t>paolorog@yahoo.it</t>
-  </si>
-  <si>
-    <t>Rogora Gabriele</t>
-  </si>
-  <si>
-    <t>rogoralele@libero.it</t>
-  </si>
-  <si>
-    <t>Sanarico Edoardo</t>
-  </si>
-  <si>
-    <t>edoardo.sanarico@icloud.com</t>
-  </si>
-  <si>
-    <t>Scudieri Luigi</t>
-  </si>
-  <si>
-    <t>luigiscudieri2@gmail.com</t>
-  </si>
-  <si>
-    <t>Scudieri Nicola</t>
-  </si>
-  <si>
-    <t>nicola.scudieri95@gmail.com</t>
-  </si>
-  <si>
-    <t>Tibichi Edwin Flavius</t>
-  </si>
-  <si>
-    <t>etibichi@yahoo.com</t>
-  </si>
-  <si>
-    <t>Traini Mauro</t>
-  </si>
-  <si>
-    <t>maurotraini59@gmail.com</t>
-  </si>
-  <si>
-    <t>Turceninoff Tatiana</t>
-  </si>
-  <si>
-    <t>turceninoff.tatiana@gmail.com</t>
-  </si>
-  <si>
-    <t>Ugarte Tacca Bruno Alejandro</t>
-  </si>
-  <si>
-    <t>ugartebruno@gmail.com</t>
-  </si>
-  <si>
-    <t>Vedovato Alessandro</t>
-  </si>
-  <si>
-    <t>a.vedovato00@gmail.com</t>
-  </si>
-  <si>
-    <t>Vignola Michele</t>
-  </si>
-  <si>
     <t>V.E.M. SRL</t>
   </si>
   <si>
@@ -1160,72 +692,6 @@
     <t>edil.bc@gmail.com</t>
   </si>
   <si>
-    <t>Argenton</t>
-  </si>
-  <si>
-    <t>Lavagna Amedeo</t>
-  </si>
-  <si>
-    <t>Pilar Iglesias</t>
-  </si>
-  <si>
-    <t>Marcì Rachele</t>
-  </si>
-  <si>
-    <t>pilar03ig@yahoo.it</t>
-  </si>
-  <si>
-    <t>rachelemar@gmail.com</t>
-  </si>
-  <si>
-    <t>brancafabio@me.com</t>
-  </si>
-  <si>
-    <t>Branca Fabio</t>
-  </si>
-  <si>
-    <t>Frignati Luca</t>
-  </si>
-  <si>
-    <t>l.frignati@libero.it</t>
-  </si>
-  <si>
-    <t>nisi.francescogiuseppe@hsr.it</t>
-  </si>
-  <si>
-    <t>Nisi Francesco</t>
-  </si>
-  <si>
-    <t>Studio Tredici Cecchin</t>
-  </si>
-  <si>
-    <t>segreteria@studiotredicicecchin.it</t>
-  </si>
-  <si>
-    <t>Castelli Alessandra</t>
-  </si>
-  <si>
-    <t>alecastle9@hotmail.com</t>
-  </si>
-  <si>
-    <t>Farioli Stefano</t>
-  </si>
-  <si>
-    <t>stefanodocfarioli@gmail.com</t>
-  </si>
-  <si>
-    <t> silvern@email.it</t>
-  </si>
-  <si>
-    <t> drlavagna@libero.it</t>
-  </si>
-  <si>
-    <t> claudia_mezzanzanica@libero.it</t>
-  </si>
-  <si>
-    <t>Mezzanzanica Claudia</t>
-  </si>
-  <si>
     <t>factorial</t>
   </si>
   <si>
@@ -1271,9 +737,6 @@
     <t>Deutsche Bank S.p.A.</t>
   </si>
   <si>
-    <t>Esti Stefano</t>
-  </si>
-  <si>
     <t>DIELLE di LEZZI DANIELE</t>
   </si>
   <si>
@@ -1379,9 +842,6 @@
     <t>igiene.ambientale@agesp.it</t>
   </si>
   <si>
-    <t>monica.andrade@outlook.it</t>
-  </si>
-  <si>
     <t>fausto@ferrarioarredamenti.it </t>
   </si>
   <si>
@@ -1433,9 +893,6 @@
     <t>AGESP SPA</t>
   </si>
   <si>
-    <t>Andraede Zambrano Monica Monserrate</t>
-  </si>
-  <si>
     <t>BIAGGINI MEDICAL DEVICES SRL</t>
   </si>
   <si>
@@ -1487,9 +944,6 @@
     <t>info@aliasdigital.it</t>
   </si>
   <si>
-    <t>stenosti@virgilio.it</t>
-  </si>
-  <si>
     <t>servizioclienti@dllgroup.com</t>
   </si>
   <si>
@@ -1523,27 +977,6 @@
     <t>stefano@confident.dental</t>
   </si>
   <si>
-    <t>Pirovano Marica</t>
-  </si>
-  <si>
-    <t>Macovei Felicia</t>
-  </si>
-  <si>
-    <t>felicia.macovei97@gmail.com</t>
-  </si>
-  <si>
-    <t>El Sayed Ahmed</t>
-  </si>
-  <si>
-    <t>dentahmed8@gmail.com</t>
-  </si>
-  <si>
-    <t>Cristallo Edoardo</t>
-  </si>
-  <si>
-    <t>edoardoc78@icloud.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">e.marzocchi@carminati.it </t>
   </si>
   <si>
@@ -1757,15 +1190,6 @@
     <t>VEODAFONE COMASINA</t>
   </si>
   <si>
-    <t>marika.newzucca@gmail.com</t>
-  </si>
-  <si>
-    <t>moozhan_7366@yahoo.com</t>
-  </si>
-  <si>
-    <t>Maghsoudlou Rad Moozhan</t>
-  </si>
-  <si>
     <t>ufficiocrediti@dentaltrey.it</t>
   </si>
   <si>
@@ -1821,9 +1245,6 @@
   </si>
   <si>
     <t>grisellimario@gmail.com</t>
-  </si>
-  <si>
-    <t>giacomo.budelli@gmail.com</t>
   </si>
   <si>
     <t>FARMACIA MP SRL</t>
@@ -2031,9 +1452,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Collegamento ipertestuale" xfId="2" builtinId="8"/>
     <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{91DD6BA5-2EDF-4C3C-B8C6-AD8592C1FB10}"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2082,7 +1503,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2399,18 +1820,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C436CF3-8B2A-4DEB-9C08-BFD6985B70D8}">
   <dimension ref="A1:H174"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" customWidth="1"/>
-    <col min="8" max="8" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.6640625" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.83203125" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" customWidth="1"/>
+    <col min="8" max="8" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2418,20 +1839,20 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>553</v>
+        <v>364</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
-        <v>580</v>
+        <v>388</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>458</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -2441,12 +1862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>462</v>
+        <v>282</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>444</v>
+        <v>265</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2456,12 +1877,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>104</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -2471,46 +1892,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" t="s">
         <v>188</v>
-      </c>
-      <c r="B5" t="s">
-        <v>189</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G5" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G6" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -2520,12 +1941,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>400</v>
+        <v>222</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -2535,12 +1956,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>403</v>
+        <v>225</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>459</v>
+        <v>279</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -2550,7 +1971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,12 +1986,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>404</v>
+        <v>226</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>460</v>
+        <v>280</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2580,41 +2001,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G12" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G13" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -2629,29 +2050,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G15" s="13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>464</v>
+        <v>283</v>
       </c>
       <c r="B16" t="s">
-        <v>433</v>
+        <v>254</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2661,9 +2082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>61</v>
@@ -2672,18 +2093,18 @@
       <c r="D17" s="1"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G17" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2693,12 +2114,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2708,27 +2129,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>405</v>
+        <v>227</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="16"/>
       <c r="F20" s="16" t="s">
-        <v>555</v>
+        <v>366</v>
       </c>
       <c r="G20" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2738,12 +2159,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>406</v>
+        <v>228</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>434</v>
+        <v>255</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2753,9 +2174,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>416</v>
+        <v>237</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -2766,32 +2187,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G24" s="13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>500</v>
+        <v>311</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>501</v>
+        <v>312</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="10"/>
@@ -2800,12 +2221,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>401</v>
+        <v>223</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2815,29 +2236,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>397</v>
+        <v>219</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G27" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2847,7 +2268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
@@ -2862,12 +2283,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="1"/>
@@ -2877,15 +2298,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>503</v>
+        <v>314</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>502</v>
+        <v>313</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="10"/>
@@ -2894,12 +2315,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>476</v>
+        <v>295</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>429</v>
+        <v>250</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="1"/>
@@ -2909,15 +2330,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>505</v>
+        <v>316</v>
       </c>
       <c r="C33" t="s">
-        <v>504</v>
+        <v>315</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="10"/>
@@ -2926,12 +2347,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>359</v>
+        <v>203</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>360</v>
+        <v>204</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="1"/>
@@ -2941,18 +2362,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>508</v>
+        <v>319</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>506</v>
+        <v>317</v>
       </c>
       <c r="D35" t="s">
-        <v>507</v>
+        <v>318</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
@@ -2960,18 +2381,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>511</v>
+        <v>322</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>510</v>
+        <v>321</v>
       </c>
       <c r="D36" t="s">
-        <v>509</v>
+        <v>320</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
@@ -2979,12 +2400,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>361</v>
+        <v>205</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>370</v>
+        <v>214</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="1"/>
@@ -2994,12 +2415,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3009,12 +2430,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>407</v>
+        <v>229</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>482</v>
+        <v>300</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -3024,15 +2445,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>513</v>
+        <v>324</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>512</v>
+        <v>323</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="10"/>
@@ -3041,37 +2462,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>574</v>
+        <v>382</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>575</v>
+        <v>383</v>
       </c>
       <c r="D41" s="18"/>
       <c r="E41" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F41" s="19"/>
       <c r="G41" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>516</v>
+        <v>327</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>514</v>
+        <v>325</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>515</v>
+        <v>326</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -3079,31 +2500,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>518</v>
+        <v>329</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>517</v>
+        <v>328</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G43" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>408</v>
+        <v>230</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>430</v>
+        <v>251</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -3113,7 +2534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
@@ -3128,12 +2549,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>410</v>
+        <v>231</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>435</v>
+        <v>256</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -3143,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>43</v>
       </c>
@@ -3158,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>10</v>
       </c>
@@ -3173,12 +2594,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3188,12 +2609,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>402</v>
+        <v>224</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>427</v>
+        <v>248</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3203,12 +2624,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>371</v>
+        <v>215</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3218,12 +2639,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3233,15 +2654,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>520</v>
+        <v>331</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>519</v>
+        <v>330</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="10"/>
@@ -3250,12 +2671,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -3265,46 +2686,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>364</v>
+        <v>208</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10" t="s">
-        <v>366</v>
+        <v>210</v>
       </c>
       <c r="G55" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>396</v>
+        <v>218</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10" t="s">
-        <v>394</v>
+        <v>216</v>
       </c>
       <c r="G56" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>474</v>
+        <v>293</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>454</v>
+        <v>274</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -3314,12 +2735,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>475</v>
+        <v>294</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>485</v>
+        <v>303</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -3329,63 +2750,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="10"/>
       <c r="F59" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G59" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="10"/>
       <c r="F60" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G60" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="10"/>
       <c r="F61" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G61" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>411</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
-        <v>453</v>
+        <v>273</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -3395,12 +2816,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>413</v>
+        <v>234</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>452</v>
+        <v>272</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -3410,12 +2831,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>412</v>
+        <v>233</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>549</v>
+        <v>360</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -3423,29 +2844,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>588</v>
+        <v>396</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="10"/>
       <c r="F65" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G65" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="18" t="s">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>576</v>
+        <v>384</v>
       </c>
       <c r="C66" s="18"/>
       <c r="D66" s="18"/>
@@ -3455,12 +2876,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>594</v>
+        <v>401</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>595</v>
+        <v>402</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -3470,12 +2891,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>590</v>
+        <v>398</v>
       </c>
       <c r="B68" t="s">
-        <v>589</v>
+        <v>397</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -3485,12 +2906,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>414</v>
+        <v>235</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>451</v>
+        <v>271</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -3500,12 +2921,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>415</v>
+        <v>236</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -3515,12 +2936,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -3530,12 +2951,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -3545,12 +2966,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>478</v>
+        <v>297</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>446</v>
+        <v>266</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -3560,7 +2981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>15</v>
       </c>
@@ -3575,12 +2996,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>418</v>
+        <v>239</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>461</v>
+        <v>281</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -3590,12 +3011,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>419</v>
+        <v>240</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>447</v>
+        <v>267</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -3605,12 +3026,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>417</v>
+        <v>238</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="C77" s="1"/>
       <c r="F77" s="10"/>
@@ -3618,12 +3039,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>473</v>
+        <v>292</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>484</v>
+        <v>302</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -3633,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>39</v>
       </c>
@@ -3646,12 +3067,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -3661,12 +3082,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
@@ -3676,12 +3097,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>465</v>
+        <v>284</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>466</v>
+        <v>285</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -3691,12 +3112,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>148</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -3706,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>23</v>
       </c>
@@ -3721,7 +3142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>12</v>
       </c>
@@ -3736,12 +3157,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B86" t="s">
-        <v>521</v>
+        <v>332</v>
       </c>
       <c r="D86" s="1"/>
       <c r="E86" s="10"/>
@@ -3750,12 +3171,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>471</v>
+        <v>290</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>431</v>
+        <v>252</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -3765,12 +3186,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="18" t="s">
-        <v>438</v>
+        <v>259</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>437</v>
+        <v>258</v>
       </c>
       <c r="C88" s="18"/>
       <c r="D88" s="18"/>
@@ -3780,15 +3201,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>578</v>
+        <v>386</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>579</v>
+        <v>387</v>
       </c>
       <c r="D89" s="18"/>
       <c r="E89" s="6" t="s">
@@ -3799,12 +3220,12 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>472</v>
+        <v>291</v>
       </c>
       <c r="B90" t="s">
         <v>45</v>
@@ -3817,7 +3238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>13</v>
       </c>
@@ -3832,35 +3253,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G92" s="13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>524</v>
+        <v>335</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>522</v>
+        <v>333</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>523</v>
+        <v>334</v>
       </c>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
@@ -3868,18 +3289,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B94" t="s">
-        <v>527</v>
+        <v>338</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>525</v>
+        <v>336</v>
       </c>
       <c r="D94" t="s">
-        <v>526</v>
+        <v>337</v>
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
@@ -3887,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>31</v>
       </c>
@@ -3902,9 +3323,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>63</v>
@@ -3917,15 +3338,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>529</v>
+        <v>340</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>528</v>
+        <v>339</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="10"/>
@@ -3934,12 +3355,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>153</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -3949,12 +3370,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B99" t="s">
         <v>154</v>
-      </c>
-      <c r="B99" t="s">
-        <v>155</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -3964,12 +3385,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>420</v>
+        <v>241</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
@@ -3979,50 +3400,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>532</v>
+        <v>343</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>530</v>
+        <v>341</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>531</v>
+        <v>342</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G101" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>369</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>368</v>
+        <v>212</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="10"/>
       <c r="F102" s="10" t="s">
-        <v>367</v>
+        <v>211</v>
       </c>
       <c r="G102" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -4032,15 +3453,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>534</v>
+        <v>345</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>533</v>
+        <v>344</v>
       </c>
       <c r="D104" s="1"/>
       <c r="E104" s="10"/>
@@ -4049,7 +3470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>16</v>
       </c>
@@ -4064,12 +3485,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>442</v>
+        <v>263</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>432</v>
+        <v>253</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -4079,12 +3500,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>581</v>
+        <v>389</v>
       </c>
       <c r="B107" t="s">
-        <v>582</v>
+        <v>390</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -4094,12 +3515,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
@@ -4109,24 +3530,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G109" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
         <v>36</v>
       </c>
@@ -4139,7 +3560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
         <v>35</v>
       </c>
@@ -4152,32 +3573,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="10"/>
       <c r="F112" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G112" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>536</v>
+        <v>347</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>535</v>
+        <v>346</v>
       </c>
       <c r="D113" s="1"/>
       <c r="E113" s="10"/>
@@ -4186,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>29</v>
       </c>
@@ -4201,12 +3622,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
@@ -4216,12 +3637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
@@ -4231,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>40</v>
       </c>
@@ -4246,7 +3667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>33</v>
       </c>
@@ -4261,12 +3682,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
@@ -4276,12 +3697,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B120" s="27" t="s">
         <v>162</v>
-      </c>
-      <c r="B120" s="27" t="s">
-        <v>163</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
@@ -4291,12 +3712,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>441</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>436</v>
+        <v>257</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
@@ -4306,15 +3727,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>538</v>
+        <v>349</v>
       </c>
       <c r="C122" s="24" t="s">
-        <v>537</v>
+        <v>348</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="10"/>
@@ -4323,12 +3744,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
@@ -4338,12 +3759,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B124" s="24" t="s">
-        <v>398</v>
+        <v>220</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
@@ -4353,12 +3774,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>470</v>
+        <v>289</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>440</v>
+        <v>261</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -4368,12 +3789,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>487</v>
+        <v>305</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -4383,29 +3804,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="10"/>
       <c r="F127" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G127" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>469</v>
+        <v>288</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>448</v>
+        <v>268</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -4415,12 +3836,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -4430,18 +3851,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>539</v>
+        <v>350</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>466</v>
+        <v>285</v>
       </c>
       <c r="D130" t="s">
-        <v>554</v>
+        <v>365</v>
       </c>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
@@ -4449,12 +3870,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>422</v>
+        <v>243</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>457</v>
+        <v>277</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
@@ -4464,15 +3885,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>541</v>
+        <v>352</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>540</v>
+        <v>351</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="23"/>
@@ -4481,12 +3902,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
@@ -4496,7 +3917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="7" t="s">
         <v>19</v>
       </c>
@@ -4505,44 +3926,44 @@
       <c r="D134" s="7"/>
       <c r="E134" s="12"/>
       <c r="F134" s="12" t="s">
-        <v>486</v>
+        <v>304</v>
       </c>
       <c r="G134" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="10"/>
       <c r="F135" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G135" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>421</v>
+        <v>242</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>542</v>
+        <v>353</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>490</v>
+        <v>308</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>489</v>
+        <v>307</v>
       </c>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
@@ -4550,12 +3971,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>551</v>
+        <v>362</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
@@ -4565,12 +3986,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>552</v>
+        <v>363</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -4580,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>14</v>
       </c>
@@ -4595,9 +4016,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>479</v>
+        <v>298</v>
       </c>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4608,18 +4029,18 @@
         <v>0</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>468</v>
+        <v>287</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>544</v>
+        <v>355</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>543</v>
+        <v>354</v>
       </c>
       <c r="D141" s="1"/>
       <c r="E141" s="10"/>
@@ -4628,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>11</v>
       </c>
@@ -4643,12 +4064,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>483</v>
+        <v>301</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>492</v>
+        <v>310</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -4658,12 +4079,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B144" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -4673,12 +4094,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
@@ -4688,12 +4109,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
@@ -4703,12 +4124,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>439</v>
+        <v>260</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>443</v>
+        <v>264</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
@@ -4718,32 +4139,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>399</v>
+        <v>221</v>
       </c>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G148" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>546</v>
+        <v>357</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>545</v>
+        <v>356</v>
       </c>
       <c r="D149" s="1"/>
       <c r="E149" s="10"/>
@@ -4752,12 +4173,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>426</v>
+        <v>247</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>456</v>
+        <v>276</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
@@ -4767,30 +4188,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="s">
-        <v>467</v>
+        <v>286</v>
       </c>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="12"/>
       <c r="F151" s="12" t="s">
-        <v>486</v>
+        <v>304</v>
       </c>
       <c r="G151" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H151" s="8" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>425</v>
+        <v>246</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>455</v>
+        <v>275</v>
       </c>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
@@ -4800,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>24</v>
       </c>
@@ -4815,15 +4236,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C154" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="D154" s="1"/>
       <c r="E154" s="10"/>
@@ -4832,12 +4253,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
@@ -4847,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>9</v>
       </c>
@@ -4862,12 +4283,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>423</v>
+        <v>244</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>449</v>
+        <v>269</v>
       </c>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
@@ -4877,12 +4298,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
@@ -4892,12 +4313,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
@@ -4907,12 +4328,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>591</v>
+        <v>399</v>
       </c>
       <c r="B160" t="s">
-        <v>592</v>
+        <v>400</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -4922,12 +4343,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>424</v>
+        <v>245</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>491</v>
+        <v>309</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
@@ -4937,12 +4358,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
@@ -4952,12 +4373,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>362</v>
+        <v>206</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>363</v>
+        <v>207</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
@@ -4967,29 +4388,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>583</v>
+        <v>391</v>
       </c>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="10"/>
       <c r="F164" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G164" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
@@ -4999,12 +4420,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>584</v>
+        <v>392</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>585</v>
+        <v>393</v>
       </c>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
@@ -5014,12 +4435,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>586</v>
+        <v>394</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>587</v>
+        <v>395</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -5029,10 +4450,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C173" s="21"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C174" s="21"/>
     </row>
   </sheetData>
@@ -5055,1095 +4476,704 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId12"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DB5288-9EC5-484E-ABAD-FEC947E6A251}">
   <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>203</v>
-      </c>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>205</v>
-      </c>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>207</v>
-      </c>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>209</v>
-      </c>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="C5" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>211</v>
-      </c>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>445</v>
-      </c>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>390</v>
-      </c>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
       <c r="C8" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>213</v>
-      </c>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>215</v>
-      </c>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
       <c r="C10" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>217</v>
-      </c>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>219</v>
-      </c>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>221</v>
-      </c>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>223</v>
-      </c>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>225</v>
-      </c>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>229</v>
-      </c>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>378</v>
-      </c>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>227</v>
-      </c>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>593</v>
-      </c>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>232</v>
-      </c>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
       <c r="C20" s="13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>234</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
       <c r="C21" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>236</v>
-      </c>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
       <c r="C22" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>387</v>
-      </c>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>238</v>
-      </c>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>240</v>
-      </c>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>242</v>
-      </c>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>244</v>
-      </c>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>246</v>
-      </c>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>248</v>
-      </c>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>499</v>
-      </c>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>250</v>
-      </c>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>252</v>
-      </c>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="24"/>
       <c r="C32" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>254</v>
-      </c>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>256</v>
-      </c>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>258</v>
-      </c>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>260</v>
-      </c>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="24"/>
       <c r="C36" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>497</v>
-      </c>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>262</v>
-      </c>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
       <c r="C38" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>481</v>
-      </c>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
       <c r="C39" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>264</v>
-      </c>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
       <c r="C40" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>389</v>
-      </c>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>266</v>
-      </c>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>381</v>
-      </c>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>268</v>
-      </c>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>270</v>
-      </c>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
       <c r="C45" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>272</v>
-      </c>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
       <c r="C46" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>274</v>
-      </c>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="24"/>
       <c r="C47" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>276</v>
-      </c>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>280</v>
-      </c>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
       <c r="C49" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>282</v>
-      </c>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
       <c r="C50" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>278</v>
-      </c>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
       <c r="C51" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>391</v>
-      </c>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
       <c r="C52" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>284</v>
-      </c>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1"/>
+      <c r="B53" s="24"/>
       <c r="C53" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>286</v>
-      </c>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="24"/>
       <c r="C54" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>495</v>
-      </c>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>573</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>572</v>
-      </c>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="18"/>
+      <c r="B56" s="25"/>
       <c r="C56" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>288</v>
-      </c>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>296</v>
-      </c>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
       <c r="C58" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>290</v>
-      </c>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="24"/>
       <c r="C59" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>292</v>
-      </c>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="24"/>
       <c r="C60" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>294</v>
-      </c>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="1"/>
+      <c r="B61" s="24"/>
       <c r="C61" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>377</v>
-      </c>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="1"/>
+      <c r="B62" s="24"/>
       <c r="C62" s="13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>298</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="1"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>392</v>
-      </c>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
       <c r="C64" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>300</v>
-      </c>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
       <c r="C65" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>318</v>
-      </c>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
       <c r="C66" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>302</v>
-      </c>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
       <c r="C67" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>304</v>
-      </c>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="1"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>306</v>
-      </c>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
       <c r="C69" s="13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>382</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
       <c r="C70" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>308</v>
-      </c>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
       <c r="C71" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>310</v>
-      </c>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
       <c r="C72" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="B73" s="24" t="s">
-        <v>312</v>
-      </c>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1"/>
+      <c r="B73" s="24"/>
       <c r="C73" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>314</v>
-      </c>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>316</v>
-      </c>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
       <c r="C75" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>320</v>
-      </c>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
       <c r="C76" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>322</v>
-      </c>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
       <c r="C77" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>376</v>
-      </c>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
       <c r="C78" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="B79" t="s">
-        <v>571</v>
-      </c>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="1"/>
       <c r="C79" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B80" s="24" t="s">
-        <v>324</v>
-      </c>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="5"/>
+      <c r="B80" s="24"/>
       <c r="C80" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B81" s="24" t="s">
-        <v>326</v>
-      </c>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="1"/>
+      <c r="B81" s="24"/>
       <c r="C81" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>328</v>
-      </c>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
       <c r="C82" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>330</v>
-      </c>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
       <c r="C83" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>332</v>
-      </c>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
       <c r="C84" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B85" s="24" t="s">
-        <v>334</v>
-      </c>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="1"/>
+      <c r="B85" s="24"/>
       <c r="C85" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>336</v>
-      </c>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
       <c r="C86" s="13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B87" s="24" t="s">
-        <v>338</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="1"/>
+      <c r="B87" s="24"/>
       <c r="C87" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>340</v>
-      </c>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
       <c r="C88" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B89" s="24" t="s">
-        <v>342</v>
-      </c>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="1"/>
+      <c r="B89" s="24"/>
       <c r="C89" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="B90" s="24" t="s">
-        <v>344</v>
-      </c>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="1"/>
+      <c r="B90" s="24"/>
       <c r="C90" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>346</v>
-      </c>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
       <c r="C91" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>385</v>
-      </c>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
       <c r="C92" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>348</v>
-      </c>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
       <c r="C93" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>350</v>
-      </c>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
       <c r="C94" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="B95" s="24" t="s">
-        <v>352</v>
-      </c>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="1"/>
+      <c r="B95" s="24"/>
       <c r="C95" s="13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>354</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
       <c r="C96" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>356</v>
-      </c>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="1"/>
+      <c r="B97" s="24"/>
       <c r="C97" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>67</v>
-      </c>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
       <c r="C98" s="13" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B98" xr:uid="{E5DB5288-9EC5-484E-ABAD-FEC947E6A251}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B98">
     <sortCondition ref="A2:A98"/>
   </sortState>
@@ -6157,187 +5187,141 @@
       <formula>$A2="N.A."</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="B12" r:id="rId1" xr:uid="{5467E679-74B8-4EB6-BC93-AFD714A67DD7}"/>
-    <hyperlink ref="B8" r:id="rId2" display="mailto:silvern@email.it" xr:uid="{2374C83D-CBF7-48F3-A7E5-982A9D28FFF1}"/>
-    <hyperlink ref="B52" r:id="rId3" display="mailto:drlavagna@libero.it" xr:uid="{F58E416E-1066-4D94-A982-C3826B7CE14E}"/>
-    <hyperlink ref="B78" r:id="rId4" display="mailto:pilar03ig@yahoo.it" xr:uid="{47FC556A-4D8E-430E-A398-CA96A6EBA77D}"/>
-    <hyperlink ref="B64" r:id="rId5" display="mailto:claudia_mezzanzanica@libero.it" xr:uid="{7D9625FD-F8A3-4D5A-96B4-98A50B3211B0}"/>
-    <hyperlink ref="B17" r:id="rId6" xr:uid="{56A50371-29FA-47BB-B355-346E322E5183}"/>
-    <hyperlink ref="B62" r:id="rId7" xr:uid="{97130FC7-ECF6-44F8-B3FA-2DB727529C6E}"/>
-    <hyperlink ref="B43" r:id="rId8" xr:uid="{7081752C-1086-49F2-9582-DE3BA28756E9}"/>
-    <hyperlink ref="B70" r:id="rId9" display="mailto:nisi.francescogiuseppe@hsr.it" xr:uid="{40BF3B3F-E376-4A61-89AB-DD573444E0D6}"/>
-    <hyperlink ref="B92" r:id="rId10" display="mailto:segreteria@studiotredicicecchin.it" xr:uid="{0736ECFB-8612-4AC4-B477-A1C7DEA65F18}"/>
-    <hyperlink ref="B23" r:id="rId11" display="mailto:alecastle9@hotmail.com" xr:uid="{5546B905-8B8C-47E8-8877-813A9E8E5AAE}"/>
-    <hyperlink ref="B41" r:id="rId12" display="mailto:stefanodocfarioli@gmail.com" xr:uid="{AC258E6E-0C19-487A-996C-F56161798415}"/>
-    <hyperlink ref="B31" r:id="rId13" xr:uid="{348956E8-D00D-4AC6-80C2-D99F8277B362}"/>
-    <hyperlink ref="B44" r:id="rId14" xr:uid="{392948D3-4188-4853-94E4-31D88376FCF5}"/>
-    <hyperlink ref="B60" r:id="rId15" xr:uid="{35A02E4A-8D9D-44EB-8521-419862CD7E67}"/>
-    <hyperlink ref="B54" r:id="rId16" xr:uid="{5775FAC4-28BE-4F1B-BD35-D18FF61A0D75}"/>
-    <hyperlink ref="B89" r:id="rId17" xr:uid="{E51C9FE3-6963-4A97-AAEB-4C8EC709DE2B}"/>
-    <hyperlink ref="B95" r:id="rId18" xr:uid="{7B080FB0-183E-4216-ADA0-BF9865796469}"/>
-    <hyperlink ref="B97" r:id="rId19" xr:uid="{16F5F474-C1C7-4860-BFC9-36CC88441C24}"/>
-    <hyperlink ref="B18" r:id="rId20" xr:uid="{EE2D4174-FA61-4A24-8895-F4CF5D9254F9}"/>
-    <hyperlink ref="B90" r:id="rId21" xr:uid="{F9867BC3-6D49-4FCF-8B67-F5194C185166}"/>
-    <hyperlink ref="B59" r:id="rId22" xr:uid="{A144D8BB-FCD5-4C45-AE2D-9E7E2BACD655}"/>
-    <hyperlink ref="B33" r:id="rId23" xr:uid="{3B264840-684E-409D-86D9-F61E2CB6A435}"/>
-    <hyperlink ref="B27" r:id="rId24" xr:uid="{CF462C30-CBDB-4856-AF27-274B4FE8F609}"/>
-    <hyperlink ref="B80" r:id="rId25" xr:uid="{28F72FCB-8A68-49B7-AB12-A7CDB0D9F035}"/>
-    <hyperlink ref="B9" r:id="rId26" xr:uid="{FE14D0C0-89FC-40D6-91E6-9175A5A04E27}"/>
-    <hyperlink ref="B14" r:id="rId27" xr:uid="{8BD31FAC-8F00-4BB3-8A9F-2CDBFB0F26B2}"/>
-    <hyperlink ref="B37" r:id="rId28" xr:uid="{E7ED7CF8-267F-4EC1-A318-65B62BF4474E}"/>
-    <hyperlink ref="B53" r:id="rId29" xr:uid="{F1C58EA6-2502-497C-96E1-7F1AC8DE710A}"/>
-    <hyperlink ref="B47" r:id="rId30" xr:uid="{8ED251F2-9BFE-41F2-9484-54385FD166EC}"/>
-    <hyperlink ref="B4" r:id="rId31" xr:uid="{416FA4C7-E1DF-49AA-84AB-D5E307E89C84}"/>
-    <hyperlink ref="B19" r:id="rId32" xr:uid="{F653815F-DEAF-4274-9521-6F579B5D1D27}"/>
-    <hyperlink ref="B63" r:id="rId33" xr:uid="{00F11F8B-F89B-485B-93A4-3F47E271B85A}"/>
-    <hyperlink ref="B11" r:id="rId34" xr:uid="{3223738E-463D-47AA-906E-B5E9D42A9924}"/>
-    <hyperlink ref="B56" r:id="rId35" xr:uid="{B76214EC-AF18-4C10-A8DC-4C3236955171}"/>
-    <hyperlink ref="B87" r:id="rId36" xr:uid="{84498352-EAEB-4DFA-804A-CCD5CD24AF57}"/>
-    <hyperlink ref="B13" r:id="rId37" xr:uid="{173E0523-EB52-4212-B1A8-56060AA9F5A8}"/>
-    <hyperlink ref="B61" r:id="rId38" xr:uid="{A450067C-A20C-4436-9AF6-F1F95BADE68F}"/>
-    <hyperlink ref="B81" r:id="rId39" xr:uid="{D376B979-CDAE-4081-BDD6-EDFB1B462AF1}"/>
-    <hyperlink ref="B85" r:id="rId40" xr:uid="{865768E8-E129-4097-A2BB-13FC9EAD5B34}"/>
-    <hyperlink ref="B68" r:id="rId41" xr:uid="{E8AC0204-9B4F-49FC-A6E2-7073A570DB39}"/>
-    <hyperlink ref="B73" r:id="rId42" xr:uid="{77869FAF-92D7-45B0-9732-412FA08A1131}"/>
-    <hyperlink ref="B48" r:id="rId43" xr:uid="{B00ED8AF-2F86-477A-9763-9D59F290E230}"/>
-    <hyperlink ref="B36" r:id="rId44" xr:uid="{80BD3D9A-5112-407A-A0AE-5EE933858AAA}"/>
-    <hyperlink ref="B32" r:id="rId45" xr:uid="{0AD93EEC-E044-4CD2-B383-491677F0CE4D}"/>
-    <hyperlink ref="B16" r:id="rId46" xr:uid="{50736019-E10E-4A5D-97F1-E2FE19835D60}"/>
-    <hyperlink ref="B35" r:id="rId47" xr:uid="{326FA1D0-4B07-473A-BFB6-CD7C38056D17}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC47955-7CEB-4423-BBDD-A1A830535978}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>556</v>
+        <v>367</v>
       </c>
       <c r="B2" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>557</v>
+        <v>368</v>
       </c>
       <c r="B3" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>558</v>
+        <v>369</v>
       </c>
       <c r="B4" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>559</v>
+        <v>370</v>
       </c>
       <c r="B5" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>560</v>
+        <v>371</v>
       </c>
       <c r="B6" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>561</v>
+        <v>372</v>
       </c>
       <c r="B7" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>562</v>
+        <v>373</v>
       </c>
       <c r="B8" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>563</v>
+        <v>374</v>
       </c>
       <c r="B9" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>564</v>
+        <v>375</v>
       </c>
       <c r="B10" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>565</v>
+        <v>376</v>
       </c>
       <c r="B11" s="13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>566</v>
+        <v>377</v>
       </c>
       <c r="B12" s="15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>567</v>
+        <v>378</v>
       </c>
       <c r="B13" s="15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>568</v>
+        <v>379</v>
       </c>
       <c r="B14" s="15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>569</v>
+        <v>380</v>
       </c>
       <c r="B15" s="15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>570</v>
+        <v>381</v>
       </c>
       <c r="B16" s="13" t="b">
         <v>0</v>
@@ -6346,5 +5330,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 This document is classified as EOLO - C2 General</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>